--- a/Excel Class Files/Part 4 Excel Functions.xlsx
+++ b/Excel Class Files/Part 4 Excel Functions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\deves\Documents\GitHub\Free_Datasets\Excel Class Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E261FF33-6F19-4CCF-BD9B-EAA96B6E5E87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FBCE2A0-BF90-4CCB-96B1-54B98CC4B029}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Functions" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="148">
   <si>
     <t>Aggregate Functions</t>
   </si>
@@ -865,6 +865,24 @@
   </si>
   <si>
     <t>Number of orders</t>
+  </si>
+  <si>
+    <t>Practice Questions</t>
+  </si>
+  <si>
+    <t>marks</t>
+  </si>
+  <si>
+    <t>Total marks</t>
+  </si>
+  <si>
+    <t>Average marks</t>
+  </si>
+  <si>
+    <t>Max marks</t>
+  </si>
+  <si>
+    <t>Min Marks</t>
   </si>
 </sst>
 </file>
@@ -988,7 +1006,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1007,8 +1025,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -1094,6 +1118,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.499984740745262"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-0.499984740745262"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1133,13 +1172,13 @@
       <alignment horizontal="left" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1481,12 +1520,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DAD343D-E03B-44D6-8F89-7D66BF329709}">
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.28515625" customWidth="1"/>
     <col min="3" max="3" width="9.85546875" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="10" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
@@ -1583,6 +1622,72 @@
       </c>
     </row>
     <row r="28" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="1:4" s="12" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A36" s="12" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B38" s="32" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B39" s="31">
+        <v>73</v>
+      </c>
+      <c r="D39" s="14" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B40" s="31">
+        <v>78</v>
+      </c>
+      <c r="D40" s="14" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B41" s="31"/>
+      <c r="D41" s="14" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B42" s="31">
+        <v>18</v>
+      </c>
+      <c r="D42" s="14" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B43" s="31">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B44" s="31"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B45" s="31">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B46" s="31"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B47" s="31">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B48" s="31">
+        <v>73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -2376,40 +2481,24 @@
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="29">
+      <c r="A18" s="27">
         <v>39295</v>
       </c>
-      <c r="B18" s="30"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="30"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="29">
+      <c r="A19" s="27">
         <v>38011</v>
       </c>
-      <c r="B19" s="30"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="29">
+      <c r="A20" s="27">
         <v>39483</v>
       </c>
-      <c r="B20" s="30"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="29">
+      <c r="A21" s="27">
         <v>37476</v>
       </c>
-      <c r="B21" s="30"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
@@ -2479,10 +2568,10 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="31" t="s">
+      <c r="A4" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="30" t="s">
         <v>81</v>
       </c>
       <c r="D4" s="14" t="s">
@@ -2490,10 +2579,10 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="30" t="s">
         <v>83</v>
       </c>
       <c r="D5" s="27">
@@ -2501,66 +2590,66 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="31" t="s">
+      <c r="A6" s="29" t="s">
         <v>84</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="30" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="31" t="s">
+      <c r="A7" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="30" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="29" t="s">
         <v>88</v>
       </c>
-      <c r="B8" s="32" t="s">
+      <c r="B8" s="30" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="31" t="s">
+      <c r="A9" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="30" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="29" t="s">
         <v>92</v>
       </c>
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="30" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="31" t="s">
+      <c r="A11" s="29" t="s">
         <v>94</v>
       </c>
-      <c r="B11" s="32" t="s">
+      <c r="B11" s="30" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="31" t="s">
+      <c r="A12" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="B12" s="32" t="s">
+      <c r="B12" s="30" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="31" t="s">
+      <c r="A13" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="B13" s="32" t="s">
+      <c r="B13" s="30" t="s">
         <v>99</v>
       </c>
     </row>
